--- a/校园招聘/制造业/制造业通用/技术研发类/机械工程师/3_需重新出题/5轮_制造业通用_机械工程师_需要重新出题.xlsx
+++ b/校园招聘/制造业/制造业通用/技术研发类/机械工程师/3_需重新出题/5轮_制造业通用_机械工程师_需要重新出题.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>制造业通用</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
